--- a/excel/国证指数成分.xlsx
+++ b/excel/国证指数成分.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="3">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8.92</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.08</v>
+        <v>6.14</v>
       </c>
     </row>
     <row r="5">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.63</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.16</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.88</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="9">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="11">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.11</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="12">
@@ -744,12 +744,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>600150</t>
+          <t>601919</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>中国船舶</t>
+          <t>中远海控</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>601919</t>
+          <t>600150</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>中远海控</t>
+          <t>中国船舶</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>601898</t>
+          <t>600170</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>中煤能源</t>
+          <t>上海建工</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -869,17 +869,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>600170</t>
+          <t>000933</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>上海建工</t>
+          <t>神火股份</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -919,17 +919,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>000933</t>
+          <t>600482</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>神火股份</t>
+          <t>中国动力</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -969,17 +969,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>600482</t>
+          <t>002532</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>中国动力</t>
+          <t>天山铝业</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -994,17 +994,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>002532</t>
+          <t>600741</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>天山铝业</t>
+          <t>华域汽车</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>600428</t>
+          <t>000959</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>中远海特</t>
+          <t>首钢股份</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>000959</t>
+          <t>600096</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>首钢股份</t>
+          <t>云天化</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>600741</t>
+          <t>600256</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>华域汽车</t>
+          <t>广汇能源</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>600096</t>
+          <t>601156</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>云天化</t>
+          <t>东航物流</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>600256</t>
+          <t>601880</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>广汇能源</t>
+          <t>辽港股份</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>601156</t>
+          <t>600428</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>东航物流</t>
+          <t>中远海特</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1169,17 +1169,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>000921</t>
+          <t>600546</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>海信家电</t>
+          <t>山煤国际</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>603233</t>
+          <t>000921</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>大参林</t>
+          <t>海信家电</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>601880</t>
+          <t>688819</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>辽港股份</t>
+          <t>天能股份</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>600546</t>
+          <t>600398</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>山煤国际</t>
+          <t>海澜之家</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>600398</t>
+          <t>600320</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>海澜之家</t>
+          <t>振华重工</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>600295</t>
+          <t>603233</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>鄂尔多斯</t>
+          <t>大参林</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>600352</t>
+          <t>600295</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>浙江龙盛</t>
+          <t>鄂尔多斯</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>688819</t>
+          <t>600060</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>天能股份</t>
+          <t>海信视像</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>600060</t>
+          <t>600352</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>海信视像</t>
+          <t>浙江龙盛</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>600320</t>
+          <t>601001</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>振华重工</t>
+          <t>晋控煤业</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>603444</t>
+          <t>600380</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>吉比特</t>
+          <t>健康元</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>603565</t>
+          <t>603883</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>中谷物流</t>
+          <t>老百姓</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>603883</t>
+          <t>000513</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>老百姓</t>
+          <t>丽珠集团</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1494,17 +1494,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>600380</t>
+          <t>600258</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>健康元</t>
+          <t>首旅酒店</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>600874</t>
+          <t>603444</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>创业环保</t>
+          <t>吉比特</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>信息技术</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>600258</t>
+          <t>600874</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>首旅酒店</t>
+          <t>创业环保</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>601083</t>
+          <t>603565</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>锦江航运</t>
+          <t>中谷物流</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1594,17 +1594,17 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>000513</t>
+          <t>601083</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>丽珠集团</t>
+          <t>锦江航运</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1619,17 +1619,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>601001</t>
+          <t>002761</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>晋控煤业</t>
+          <t>浙江建投</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>603766</t>
+          <t>600033</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>隆鑫通用</t>
+          <t>福建高速</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>002761</t>
+          <t>603766</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>浙江建投</t>
+          <t>隆鑫通用</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>600033</t>
+          <t>300244</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>福建高速</t>
+          <t>迪安诊断</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>600267</t>
+          <t>002039</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>海正药业</t>
+          <t>黔源电力</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>000400</t>
+          <t>601827</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>许继电气</t>
+          <t>三峰环境</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>002039</t>
+          <t>000400</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>黔源电力</t>
+          <t>许继电气</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>300244</t>
+          <t>600163</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>迪安诊断</t>
+          <t>中闽能源</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>600729</t>
+          <t>002545</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>重百集团</t>
+          <t>东方铁塔</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>002545</t>
+          <t>600267</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>东方铁塔</t>
+          <t>海正药业</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>002004</t>
+          <t>600729</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>华邦健康</t>
+          <t>重百集团</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>000957</t>
+          <t>000719</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>中通客车</t>
+          <t>中原传媒</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>000719</t>
+          <t>002004</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>中原传媒</t>
+          <t>华邦健康</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>000090</t>
+          <t>002416</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>天健集团</t>
+          <t>爱施德</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2019,17 +2019,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>002727</t>
+          <t>000957</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>一心堂</t>
+          <t>中通客车</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>600163</t>
+          <t>000090</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>中闽能源</t>
+          <t>天健集团</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>002416</t>
+          <t>002061</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>爱施德</t>
+          <t>浙江交科</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>002061</t>
+          <t>002727</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>浙江交科</t>
+          <t>一心堂</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>002170</t>
+          <t>000690</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>芭田股份</t>
+          <t>宝新能源</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>000690</t>
+          <t>002170</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>宝新能源</t>
+          <t>芭田股份</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2219,17 +2219,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>002697</t>
+          <t>000915</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>红旗连锁</t>
+          <t>华特达因</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>000597</t>
+          <t>688128</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>东北制药</t>
+          <t>中国电研</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>301039</t>
+          <t>002697</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>中集车辆</t>
+          <t>红旗连锁</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>000915</t>
+          <t>301039</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>华特达因</t>
+          <t>中集车辆</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2319,17 +2319,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>603708</t>
+          <t>000597</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>家家悦</t>
+          <t>东北制药</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2344,17 +2344,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>600195</t>
+          <t>600686</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>中牧股份</t>
+          <t>金龙汽车</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2369,17 +2369,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>002043</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>兔 宝 宝</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2394,17 +2394,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>002043</t>
+          <t>603661</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>兔 宝 宝</t>
+          <t>恒林股份</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>600686</t>
+          <t>600195</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>金龙汽车</t>
+          <t>中牧股份</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>603368</t>
+          <t>601801</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>柳药集团</t>
+          <t>皖新传媒</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2469,17 +2469,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>603173</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>福斯达</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>601801</t>
+          <t>603279</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>皖新传媒</t>
+          <t>景津装备</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>000650</t>
+          <t>001338</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>仁和药业</t>
+          <t>永顺泰</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2544,17 +2544,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>001338</t>
+          <t>600449</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>永顺泰</t>
+          <t>宁夏建材</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>688330</t>
+          <t>000650</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>宏力达</t>
+          <t>仁和药业</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2594,17 +2594,17 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>603279</t>
+          <t>605377</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>景津装备</t>
+          <t>华旺科技</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2619,17 +2619,17 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>605377</t>
+          <t>688330</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>华旺科技</t>
+          <t>宏力达</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2669,17 +2669,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>600897</t>
+          <t>300389</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>厦门空港</t>
+          <t>艾比森</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>信息技术</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2694,17 +2694,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>600351</t>
+          <t>002478</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>亚宝药业</t>
+          <t>常宝股份</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>002478</t>
+          <t>002918</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>常宝股份</t>
+          <t>蒙娜丽莎</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>002918</t>
+          <t>600351</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>蒙娜丽莎</t>
+          <t>亚宝药业</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2769,17 +2769,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>601002</t>
+          <t>300349</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>晋亿实业</t>
+          <t>金卡智能</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>信息技术</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2794,17 +2794,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>300389</t>
+          <t>300228</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>艾比森</t>
+          <t>富瑞特装</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>002081</t>
+          <t>000551</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>金 螳 螂</t>
+          <t>创元科技</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>300228</t>
+          <t>601002</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>富瑞特装</t>
+          <t>晋亿实业</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>300349</t>
+          <t>002081</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>金卡智能</t>
+          <t>金 螳 螂</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>000551</t>
+          <t>002454</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>创元科技</t>
+          <t>松芝股份</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>002454</t>
+          <t>002375</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>松芝股份</t>
+          <t>亚厦股份</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">

--- a/excel/国证指数成分.xlsx
+++ b/excel/国证指数成分.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.18</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="3">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9.08</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="4">
@@ -535,12 +535,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>000651</t>
+          <t>600104</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>格力电器</t>
+          <t>上汽集团</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.14</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="5">
@@ -558,12 +558,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>600104</t>
+          <t>000651</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>上汽集团</t>
+          <t>格力电器</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.13</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.68</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.07</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="9">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="10">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="11">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="12">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>601156</t>
+          <t>601880</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>东航物流</t>
+          <t>辽港股份</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>601880</t>
+          <t>601156</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>辽港股份</t>
+          <t>东航物流</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>600398</t>
+          <t>603233</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>海澜之家</t>
+          <t>大参林</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>603233</t>
+          <t>600398</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>大参林</t>
+          <t>海澜之家</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>600060</t>
+          <t>600352</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>海信视像</t>
+          <t>浙江龙盛</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>600352</t>
+          <t>600060</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>浙江龙盛</t>
+          <t>海信视像</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>601001</t>
+          <t>600380</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>晋控煤业</t>
+          <t>健康元</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>600380</t>
+          <t>000513</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>健康元</t>
+          <t>丽珠集团</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>603883</t>
+          <t>601001</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>老百姓</t>
+          <t>晋控煤业</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>000513</t>
+          <t>603883</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>丽珠集团</t>
+          <t>老百姓</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>601083</t>
+          <t>002761</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>锦江航运</t>
+          <t>浙江建投</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>002761</t>
+          <t>601083</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>浙江建投</t>
+          <t>锦江航运</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>603766</t>
+          <t>002039</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>隆鑫通用</t>
+          <t>黔源电力</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>300244</t>
+          <t>603766</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>迪安诊断</t>
+          <t>隆鑫通用</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>002039</t>
+          <t>000400</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>黔源电力</t>
+          <t>许继电气</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>601827</t>
+          <t>300244</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>三峰环境</t>
+          <t>迪安诊断</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>000400</t>
+          <t>601827</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>许继电气</t>
+          <t>三峰环境</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>600163</t>
+          <t>600004</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>中闽能源</t>
+          <t>白云机场</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>600004</t>
+          <t>600163</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>白云机场</t>
+          <t>中闽能源</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1844,17 +1844,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>002545</t>
+          <t>600267</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>东方铁塔</t>
+          <t>海正药业</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>600267</t>
+          <t>600729</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>海正药业</t>
+          <t>重百集团</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>600729</t>
+          <t>000719</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>重百集团</t>
+          <t>中原传媒</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>000719</t>
+          <t>002545</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>中原传媒</t>
+          <t>东方铁塔</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -1944,17 +1944,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>601339</t>
+          <t>002004</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>百隆东方</t>
+          <t>华邦健康</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -1969,17 +1969,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>002004</t>
+          <t>601339</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>华邦健康</t>
+          <t>百隆东方</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>002416</t>
+          <t>000957</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>爱施德</t>
+          <t>中通客车</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2019,17 +2019,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>000957</t>
+          <t>000090</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>中通客车</t>
+          <t>天健集团</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>000090</t>
+          <t>002416</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>天健集团</t>
+          <t>爱施德</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>002204</t>
+          <t>000690</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>大连重工</t>
+          <t>宝新能源</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>000690</t>
+          <t>002204</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>宝新能源</t>
+          <t>大连重工</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2219,17 +2219,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>000915</t>
+          <t>002697</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>华特达因</t>
+          <t>红旗连锁</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>688128</t>
+          <t>000915</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>中国电研</t>
+          <t>华特达因</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>002697</t>
+          <t>688128</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>红旗连锁</t>
+          <t>中国电研</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2394,17 +2394,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>603661</t>
+          <t>600195</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>恒林股份</t>
+          <t>中牧股份</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>600195</t>
+          <t>601801</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>中牧股份</t>
+          <t>皖新传媒</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>601801</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>皖新传媒</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2469,17 +2469,17 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>603279</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>景津装备</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>603279</t>
+          <t>001338</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>景津装备</t>
+          <t>永顺泰</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>001338</t>
+          <t>603661</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>永顺泰</t>
+          <t>恒林股份</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2694,17 +2694,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>002478</t>
+          <t>002918</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>常宝股份</t>
+          <t>蒙娜丽莎</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>002918</t>
+          <t>600351</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>蒙娜丽莎</t>
+          <t>亚宝药业</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>600351</t>
+          <t>002478</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>亚宝药业</t>
+          <t>常宝股份</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>000026</t>
+          <t>002454</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>飞亚达</t>
+          <t>松芝股份</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>000551</t>
+          <t>601002</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>创元科技</t>
+          <t>晋亿实业</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>601002</t>
+          <t>000551</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>晋亿实业</t>
+          <t>创元科技</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>002081</t>
+          <t>000026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>金 螳 螂</t>
+          <t>飞亚达</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>002454</t>
+          <t>002081</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>松芝股份</t>
+          <t>金 螳 螂</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">

--- a/excel/国证指数成分.xlsx
+++ b/excel/国证指数成分.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.29</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="3">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9.18</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.17</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="5">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.06</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.57</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="7">
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.21</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="8">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.97</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="9">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="10">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="11">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="12">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>600320</t>
+          <t>600398</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>振华重工</t>
+          <t>海澜之家</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>600398</t>
+          <t>600320</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>海澜之家</t>
+          <t>振华重工</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>000513</t>
+          <t>601001</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>丽珠集团</t>
+          <t>晋控煤业</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>601001</t>
+          <t>000513</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>晋控煤业</t>
+          <t>丽珠集团</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1494,17 +1494,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>600258</t>
+          <t>600874</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>首旅酒店</t>
+          <t>创业环保</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>600874</t>
+          <t>600258</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>创业环保</t>
+          <t>首旅酒店</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>600033</t>
+          <t>002039</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>福建高速</t>
+          <t>黔源电力</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1669,17 +1669,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>002039</t>
+          <t>600033</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>黔源电力</t>
+          <t>福建高速</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>603766</t>
+          <t>000400</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>隆鑫通用</t>
+          <t>许继电气</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>000400</t>
+          <t>603766</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>许继电气</t>
+          <t>隆鑫通用</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>300244</t>
+          <t>601827</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>迪安诊断</t>
+          <t>三峰环境</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1769,17 +1769,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>601827</t>
+          <t>300244</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>三峰环境</t>
+          <t>迪安诊断</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1794,17 +1794,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>600004</t>
+          <t>600163</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>白云机场</t>
+          <t>中闽能源</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1819,17 +1819,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>600163</t>
+          <t>600004</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>中闽能源</t>
+          <t>白云机场</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>000957</t>
+          <t>000690</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>中通客车</t>
+          <t>宝新能源</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2019,17 +2019,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>000090</t>
+          <t>000957</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>天健集团</t>
+          <t>中通客车</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>002061</t>
+          <t>000090</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>浙江交科</t>
+          <t>天健集团</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>002727</t>
+          <t>002061</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>一心堂</t>
+          <t>浙江交科</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>000690</t>
+          <t>002727</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>宝新能源</t>
+          <t>一心堂</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2419,17 +2419,17 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>601801</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>皖新传媒</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>601801</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>皖新传媒</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>001338</t>
+          <t>603661</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>永顺泰</t>
+          <t>恒林股份</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>603661</t>
+          <t>001338</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>恒林股份</t>
+          <t>永顺泰</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2669,17 +2669,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>300389</t>
+          <t>002918</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>艾比森</t>
+          <t>蒙娜丽莎</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2694,17 +2694,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>002918</t>
+          <t>300389</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>蒙娜丽莎</t>
+          <t>艾比森</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>信息技术</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2769,17 +2769,17 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>300349</t>
+          <t>300228</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>金卡智能</t>
+          <t>富瑞特装</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2794,17 +2794,17 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>300228</t>
+          <t>300349</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>富瑞特装</t>
+          <t>金卡智能</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>信息技术</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">

--- a/excel/国证指数成分.xlsx
+++ b/excel/国证指数成分.xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.46</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="3">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9.33</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -535,12 +535,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>600104</t>
+          <t>000651</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>上汽集团</t>
+          <t>格力电器</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.16</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="5">
@@ -558,12 +558,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>000651</t>
+          <t>600104</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>格力电器</t>
+          <t>上汽集团</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.03</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="6">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>5.4</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="7">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="9">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="11">
@@ -696,21 +696,21 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>000338</t>
+          <t>601225</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>潍柴动力</t>
+          <t>陕西煤业</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -719,17 +719,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>601225</t>
+          <t>000338</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>陕西煤业</t>
+          <t>潍柴动力</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>601880</t>
+          <t>601156</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>辽港股份</t>
+          <t>东航物流</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>601156</t>
+          <t>601880</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>东航物流</t>
+          <t>辽港股份</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>600428</t>
+          <t>600546</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>中远海特</t>
+          <t>山煤国际</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1169,17 +1169,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>600546</t>
+          <t>600428</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>山煤国际</t>
+          <t>中远海特</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>能源</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>600060</t>
+          <t>600380</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>海信视像</t>
+          <t>健康元</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>600380</t>
+          <t>600060</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>健康元</t>
+          <t>海信视像</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1494,17 +1494,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>600874</t>
+          <t>603444</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>创业环保</t>
+          <t>吉比特</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>信息技术</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>603444</t>
+          <t>600874</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>吉比特</t>
+          <t>创业环保</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>000400</t>
+          <t>601827</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>许继电气</t>
+          <t>三峰环境</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>603766</t>
+          <t>000400</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>隆鑫通用</t>
+          <t>许继电气</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>601827</t>
+          <t>603766</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>三峰环境</t>
+          <t>隆鑫通用</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>002545</t>
+          <t>002004</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>东方铁塔</t>
+          <t>华邦健康</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>002004</t>
+          <t>002545</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>华邦健康</t>
+          <t>东方铁塔</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1994,17 +1994,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>000690</t>
+          <t>002416</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>宝新能源</t>
+          <t>爱施德</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2019,17 +2019,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>000957</t>
+          <t>000690</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>中通客车</t>
+          <t>宝新能源</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>002416</t>
+          <t>000957</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>爱施德</t>
+          <t>中通客车</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2094,17 +2094,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>002061</t>
+          <t>002727</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>浙江交科</t>
+          <t>一心堂</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>002727</t>
+          <t>002061</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>一心堂</t>
+          <t>浙江交科</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>688128</t>
+          <t>000597</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>中国电研</t>
+          <t>东北制药</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2319,17 +2319,17 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>000597</t>
+          <t>002043</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>东北制药</t>
+          <t>兔 宝 宝</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2344,17 +2344,17 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>600686</t>
+          <t>688128</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>金龙汽车</t>
+          <t>中国电研</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2369,17 +2369,17 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>002043</t>
+          <t>600686</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>兔 宝 宝</t>
+          <t>金龙汽车</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2394,17 +2394,17 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>600195</t>
+          <t>601801</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>中牧股份</t>
+          <t>皖新传媒</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>600300</t>
+          <t>600195</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>维维股份</t>
+          <t>中牧股份</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>601801</t>
+          <t>600300</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>皖新传媒</t>
+          <t>维维股份</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2494,17 +2494,17 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>603661</t>
+          <t>001338</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>恒林股份</t>
+          <t>永顺泰</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>可选消费</t>
+          <t>主要消费</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2519,17 +2519,17 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>001338</t>
+          <t>603661</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>永顺泰</t>
+          <t>恒林股份</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>主要消费</t>
+          <t>可选消费</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2544,17 +2544,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>600449</t>
+          <t>000650</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>宁夏建材</t>
+          <t>仁和药业</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>000650</t>
+          <t>600449</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>仁和药业</t>
+          <t>宁夏建材</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2669,17 +2669,17 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>002918</t>
+          <t>600351</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>蒙娜丽莎</t>
+          <t>亚宝药业</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>工业</t>
+          <t>医药卫生</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2694,17 +2694,17 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>300389</t>
+          <t>002918</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>艾比森</t>
+          <t>蒙娜丽莎</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>信息技术</t>
+          <t>工业</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>600351</t>
+          <t>300389</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>亚宝药业</t>
+          <t>艾比森</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>医药卫生</t>
+          <t>信息技术</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
